--- a/Day 1_Manual Testing/Sayan_Saha_Magicbricks_Group4.xlsx
+++ b/Day 1_Manual Testing/Sayan_Saha_Magicbricks_Group4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75D24235-8A58-4EF3-9ABC-2947CCA6BF32}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA19A565-E65F-4C55-958E-1FD2A59180EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="11496" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User Story_Edited" sheetId="8" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="400">
   <si>
     <t>Issue Type</t>
   </si>
@@ -456,102 +456,49 @@
     <t>Verify PG tab switches to PG-specific filters including Gender Preference and hides Property Type and BHK filters</t>
   </si>
   <si>
-    <t>TC-028</t>
-  </si>
-  <si>
-    <t>TC-029</t>
-  </si>
-  <si>
     <t>SS-15</t>
   </si>
   <si>
     <t>Verify Plot tab shows area-based filters, excludes BHK filter, and returns only Plot/Land type listings</t>
   </si>
   <si>
-    <t>TC-030</t>
-  </si>
-  <si>
-    <t>TC-031</t>
-  </si>
-  <si>
     <t>SS-16</t>
   </si>
   <si>
     <t>Verify Commercial tab displays Rent/Lease sub-options with Office Space Type filter and returns only commercial listings</t>
   </si>
   <si>
-    <t>TC-032</t>
-  </si>
-  <si>
-    <t>1. Navigate to Commercial tab results
-2. Carefully scan first 20 listing cards
-3. Look for any Flat, House, Villa, or Plot listing</t>
-  </si>
-  <si>
     <t>End-to-End User Journey &amp; Functional Validation of Buy Module in MagicBricks Website</t>
   </si>
   <si>
     <t>As a homebuyer, I want to explore and purchase properties that are trending or popular in my area, so that I can make a confident investment choice based on community trends and high demand</t>
   </si>
   <si>
-    <t>SS-01: Ready to Move — Property Discovery &amp; Filter Validation</t>
-  </si>
-  <si>
-    <t>SS-02: Owner Properties — Direct Contact &amp; Broker Exclusion</t>
-  </si>
-  <si>
-    <t>SS-03: Budget Homes — Affordability-Driven Search &amp; EMI Estimation</t>
-  </si>
-  <si>
     <t>Sub Story 4</t>
   </si>
   <si>
-    <t>SS-04: Premium Homes — Luxury Segment Discovery &amp; Quality Assurance</t>
-  </si>
-  <si>
     <t>Sub Story 5</t>
   </si>
   <si>
-    <t>SS-05: New Projects — Launch Discovery, RERA Compliance &amp; Lead Capture</t>
-  </si>
-  <si>
     <t>As a potential property buyer, I want to filter and browse properties by specific types (e.g., apartment, villa, commercial shop, plot) so that I can quickly find options that match my specific needs</t>
   </si>
   <si>
     <t>Sub Story 6</t>
   </si>
   <si>
-    <t>SS-06: Flats in Mumbai — Residential Apartment Search &amp; Filter Validation</t>
-  </si>
-  <si>
     <t>Sub Story 7</t>
   </si>
   <si>
-    <t>SS-07: House for Sale in Mumbai — Independent Dwelling Search &amp; Map Integration</t>
-  </si>
-  <si>
     <t>Sub Story 8</t>
   </si>
   <si>
-    <t>SS-08: Villa in Mumbai — Luxury Independent Property Browsing &amp; Detail Accuracy</t>
-  </si>
-  <si>
     <t>Sub Story 9</t>
   </si>
   <si>
-    <t>SS-09: Plot in Mumbai — Land/Plot Search, Dimension Display &amp; BHK Exclusion</t>
-  </si>
-  <si>
     <t>Sub Story 10</t>
   </si>
   <si>
-    <t>SS-10: Office Space in Mumbai — Commercial Property Search &amp; Lead Generation</t>
-  </si>
-  <si>
     <t>Sub Story 11</t>
-  </si>
-  <si>
-    <t>SS-11: Commercial Space in Mumbai — Multi-Subtype Browsing, Sorting &amp; Pagination</t>
   </si>
   <si>
     <t>As a buyer/tenant/visitor, I want to use a search bar to find properties by keyword, so that I can easily locate items I am interested in without browsing the entire catalog</t>
@@ -601,9 +548,6 @@
   <si>
     <t>Status Iteration 2
 (update only if failed in Iter 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-01  ·  Story 1: Popular Choices  ·  Verify 'Ready to Move' filter loads results showing only properties with immediate possession</t>
   </si>
   <si>
     <t>Verify 'Ready to Move' filter loads results showing only properties with immediate possession</t>
@@ -629,24 +573,6 @@
     <t>Results page loads with 'Ready to Move' filter chip active. All 5 inspected cards show 'Ready to Move' possession tag. URL contains possession filter param.</t>
   </si>
   <si>
-    <t>Under Construction or future-possession listings must NOT appear in Ready to Move results</t>
-  </si>
-  <si>
-    <t>1. Navigate to Ready to Move results page
-2. Scroll through all visible listing cards on page 1 and page 2
-3. Look for any card showing 'Under Construction' or a future possession date</t>
-  </si>
-  <si>
-    <t>URL: Ready to Move results page
-Search: Page 1 and Page 2 listing cards</t>
-  </si>
-  <si>
-    <t>Zero Under Construction or future-possession listings appear on any page. Filter is strictly enforced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-02  ·  Story 1: Popular Choices  ·  Verify Owner Properties displays only owner-listed properties and phone reveal requires authentication</t>
-  </si>
-  <si>
     <t>Verify Owner Properties displays only owner-listed properties and phone reveal requires authentication</t>
   </si>
   <si>
@@ -684,9 +610,6 @@
   </si>
   <si>
     <t>Login/signup modal appears. Phone number NOT revealed. Zero Broker or Agent tagged listings appear in results.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-03  ·  Story 1: Popular Choices  ·  Verify Budget Homes enforces price ceiling and EMI Calculator computes correctly</t>
   </si>
   <si>
     <t>Verify Budget Homes enforces price ceiling and EMI Calculator computes correctly</t>
@@ -730,9 +653,6 @@
     <t>Entering 0 shows 'Enter a valid loan amount greater than 0'. Alphabetic input in interest rate is rejected. No EMI value calculated. No NaN displayed.</t>
   </si>
   <si>
-    <t xml:space="preserve">  SS-04  ·  Story 1: Popular Choices  ·  Verify Premium Homes shows only luxury-tier listings and image gallery navigation functions correctly</t>
-  </si>
-  <si>
     <t>Verify Premium Homes shows only luxury-tier listings and image gallery navigation functions correctly</t>
   </si>
   <si>
@@ -753,25 +673,6 @@
   </si>
   <si>
     <t>All 3 cards priced above the luxury threshold. Gallery cycles correctly. Counter updates on each click (e.g. 1/10 → 2/10 → 3/10 → 4/10). Images load within 3 seconds.</t>
-  </si>
-  <si>
-    <t>Budget listings must not appear in Premium Homes; single-image listings must disable gallery arrows</t>
-  </si>
-  <si>
-    <t>1. Navigate to Premium Homes results
-2. Look for any listing priced below ₹50L or tagged 'Budget'
-3. Open a Premium listing that has only 1 image
-4. Check for next/prev arrows</t>
-  </si>
-  <si>
-    <t>City: Mumbai
-Listing: Single-image Premium property</t>
-  </si>
-  <si>
-    <t>Zero budget listings found. On single-image listing, next/prev arrows are hidden or disabled. Counter shows '1/1'. No JS error.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-05  ·  Story 1: Popular Choices  ·  Verify New Projects cards show mandatory fields and enquiry form validates mobile number before submission</t>
   </si>
   <si>
     <t>Verify New Projects cards show mandatory fields and enquiry form validates mobile number before submission</t>
@@ -816,9 +717,6 @@
     <t>Form submission blocked. Validation error 'Mobile number is required' shown. Field highlighted in error state. No lead sent to builder.</t>
   </si>
   <si>
-    <t xml:space="preserve">  SS-06  ·  Story 2: Property Types  ·  Verify Flats in Mumbai results contain only Flat/Apartment type listings and BHK + budget filters combine correctly</t>
-  </si>
-  <si>
     <t>Verify Flats in Mumbai results contain only Flat/Apartment type listings and BHK + budget filters combine correctly</t>
   </si>
   <si>
@@ -842,24 +740,6 @@
     <t>Heading reads 'Flats for Sale in Mumbai'. All 5 cards are Flat/Apartment type. After applying filters, results show only 2 BHK flats priced ₹50L–₹1Cr. Both filter chips active.</t>
   </si>
   <si>
-    <t>No Villa, Plot, or Commercial listings must appear in Flats in Mumbai results</t>
-  </si>
-  <si>
-    <t>1. Navigate to Flats in Mumbai results
-2. Systematically scan first 20 listing cards
-3. Look for any Villa, Plot, Office, or Commercial property type label</t>
-  </si>
-  <si>
-    <t>City: Mumbai
-Results: First 20 listing cards</t>
-  </si>
-  <si>
-    <t>Zero non-flat property types appear. Villa, Plot, and Commercial listings completely absent. Filter strictly enforced.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-07  ·  Story 2: Property Types  ·  Verify House for Sale in Mumbai shows only independent dwellings and Map View renders property pins correctly</t>
-  </si>
-  <si>
     <t>Verify House for Sale in Mumbai shows only independent dwellings and Map View renders property pins correctly</t>
   </si>
   <si>
@@ -883,25 +763,6 @@
     <t>All 5 cards show Independent House / Builder Floor type. Map loads within 3 seconds. Clicking a pin shows mini-card with image, price, area, and 'View Details' CTA.</t>
   </si>
   <si>
-    <t>Map View must show empty state when no results match applied filters</t>
-  </si>
-  <si>
-    <t>1. Apply filters on House for Sale results yielding zero listings
-2. Switch to Map View
-3. Observe map state and messaging</t>
-  </si>
-  <si>
-    <t>City: Mumbai
-Filter: Combination yielding zero results
-View: Map View</t>
-  </si>
-  <si>
-    <t>Map tiles render correctly. Empty state message shown: 'No properties to show for current filters'. No blank white canvas. No JS error.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-08  ·  Story 2: Property Types  ·  Verify Villa in Mumbai results show only villa-type listings with villa-specific detail fields</t>
-  </si>
-  <si>
     <t>Verify Villa in Mumbai results show only villa-type listings with villa-specific detail fields</t>
   </si>
   <si>
@@ -917,24 +778,6 @@
   </si>
   <si>
     <t>Results show only Villa type listings. Both detail pages display plot area, number of floors, facing direction, private garden (Yes/No), and number of car parks.</t>
-  </si>
-  <si>
-    <t>No flat or apartment listings must appear; floor plan unavailability must be handled gracefully</t>
-  </si>
-  <si>
-    <t>1. Scan Villa results for any Studio Apartment or Flat listing
-2. Open a Villa listing where no floor plan is uploaded
-3. Click the Floor Plan tab</t>
-  </si>
-  <si>
-    <t>City: Mumbai
-Listing: Villa with no floor plan uploaded</t>
-  </si>
-  <si>
-    <t>Zero flat or apartment listings present. Floor Plan tab shows 'Floor plan not available for this property'. No broken image icon. No blank space.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-09  ·  Story 2: Property Types  ·  Verify Plot in Mumbai has no BHK filter and detail pages display plot-specific fields including dimensions and zone type</t>
   </si>
   <si>
     <t>Verify Plot in Mumbai has no BHK filter and detail pages display plot-specific fields including dimensions and zone type</t>
@@ -968,13 +811,7 @@
 3. Reload the page and check results</t>
   </si>
   <si>
-    <t>URL manipulation: &amp;bhk=2 added to Plot results URL</t>
-  </si>
-  <si>
     <t>No built-up or apartment-type properties appear. System ignores BHK param for plot results or returns 0 results with a message. Plot filter not overridden.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-10  ·  Story 2: Property Types  ·  Verify Office Space in Mumbai shows only commercial listings with commercial-specific filters and validates enquiry form</t>
   </si>
   <si>
     <t>Verify Office Space in Mumbai shows only commercial listings with commercial-specific filters and validates enquiry form</t>
@@ -1011,9 +848,6 @@
     <t>Form not submitted. Validation error 'Please enter a valid 10-digit mobile number' shown. Phone field highlighted with error styling. No lead created in system.</t>
   </si>
   <si>
-    <t xml:space="preserve">  SS-11  ·  Story 2: Property Types  ·  Verify Commercial Space in Mumbai supports sub-type filtering and sort order persists across pagination</t>
-  </si>
-  <si>
     <t>Verify Commercial Space in Mumbai supports sub-type filtering and sort order persists across pagination</t>
   </si>
   <si>
@@ -1037,23 +871,6 @@
     <t>Only Shop listings shown. Page 1 results in descending price order. Page 2 loads with prices lower than page 1's last listing. Sort and filter chips remain active.</t>
   </si>
   <si>
-    <t>Invalid page number in URL must not throw server error</t>
-  </si>
-  <si>
-    <t>1. On Commercial Space results page
-2. Manually edit URL to set page=9999
-3. Load the page and observe response</t>
-  </si>
-  <si>
-    <t>URL: Commercial Space results with page=9999</t>
-  </si>
-  <si>
-    <t>Last valid page OR clean empty state displayed. No HTTP 500 server error. Navigation controls (Previous, First page) still function correctly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-12  ·  Story 3: Search Bar  ·  Verify Buy tab in search bar is active by default with correct sale filters and restores correctly after tab switch</t>
-  </si>
-  <si>
     <t>Verify Buy tab in search bar is active by default with correct sale filters and restores correctly after tab switch</t>
   </si>
   <si>
@@ -1074,25 +891,6 @@
   </si>
   <si>
     <t>Buy tab is highlighted on page load. category=S in URL. After Rent→Buy switch, category returns to S. Filters shown: Location, Property Type, Budget Min–Max.</t>
-  </si>
-  <si>
-    <t>Buy tab must remain active after page refresh — category=S must be preserved in URL</t>
-  </si>
-  <si>
-    <t>1. Open results page with category=S in URL
-2. Do NOT click any tab
-3. Press F5 to hard refresh
-4. Check which tab is active and the URL param</t>
-  </si>
-  <si>
-    <t>URL: category=S
-Action: Hard refresh (F5)</t>
-  </si>
-  <si>
-    <t>After refresh, Buy tab remains active. category=S preserved in URL. Results still show sale listings. No accidental switch to Rent or any other tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-13  ·  Story 3: Search Bar  ·  Verify Rent tab switches context to rental listings with updated URL param and rent-specific Budget filter label</t>
   </si>
   <si>
     <t>User is on MagicBricks residential results page. Search bar is visible. Buy tab is currently active.</t>
@@ -1115,26 +913,6 @@
     <t>URL param changes to category=R. Page heading shows 'for Rent'. Budget filter label reads 'Rent/Month'. All 3 cards show monthly rent price, not sale price.</t>
   </si>
   <si>
-    <t>Switching Buy→Rent must retain location but reset the budget range</t>
-  </si>
-  <si>
-    <t>1. Enter location 'Gachibowli' in the Location filter under Buy tab
-2. Set a budget range ₹50L–₹1Cr
-3. Switch to Rent tab
-4. Observe the location and budget field values</t>
-  </si>
-  <si>
-    <t>Location: Gachibowli
-Budget set: ₹50L–₹1Cr
-Action: Switch to Rent tab</t>
-  </si>
-  <si>
-    <t>Location 'Gachibowli' is retained after switching to Rent tab. Budget range is reset — stale sale budget value not carried over to Rent context.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-14  ·  Story 3: Search Bar  ·  Verify PG tab shows PG-specific filters including Gender Preference and hides BHK and Property Type filters</t>
-  </si>
-  <si>
     <t>Verify PG tab shows PG-specific filters including Gender Preference and hides BHK and Property Type filters</t>
   </si>
   <si>
@@ -1158,25 +936,6 @@
     <t>Filters show: Location, Gender Preference (Male/Female/Co-ed), Monthly Rent range. BHK and Property Type filters absent. All 3 result cards show PG/co-living accommodations.</t>
   </si>
   <si>
-    <t>Searching PG in area with no listings must show a graceful empty state</t>
-  </si>
-  <si>
-    <t>1. Click PG tab
-2. Select a locality where no PG listings exist
-3. Execute the search
-4. Observe results page</t>
-  </si>
-  <si>
-    <t>Tab: PG
-Location: Remote area with no PG listings</t>
-  </si>
-  <si>
-    <t>Empty state shown: 'No PG accommodations found in [Location]'. Suggestion to try a nearby area. No blank page or broken layout. Search bar remains accessible.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  SS-15  ·  Story 3: Search Bar  ·  Verify Plot tab shows area-based filters, excludes BHK filter, and returns only Plot/Land type listings</t>
-  </si>
-  <si>
     <t>User is on MagicBricks search bar. Plot tab is accessible. Plot listings are available in the selected city.</t>
   </si>
   <si>
@@ -1213,9 +972,6 @@
     <t>Search not executed. Validation error: 'Minimum area cannot be greater than maximum area'. Fields highlighted in error state. No results loaded.</t>
   </si>
   <si>
-    <t xml:space="preserve">  SS-16  ·  Story 3: Search Bar  ·  Verify Commercial tab shows Rent/Lease sub-options with Office Space Type filter and returns only commercial listings</t>
-  </si>
-  <si>
     <t>Verify Commercial tab shows Rent/Lease sub-options with Office Space Type filter and returns only commercial listings</t>
   </si>
   <si>
@@ -1239,62 +995,168 @@
     <t>Rent and Lease sub-options visible. Office Space Type filter shows: Office, Shop, Showroom, Warehouse, Co-working. After selecting Warehouse, all 5 cards show Warehouse type only.</t>
   </si>
   <si>
-    <t>No residential listings must appear in Commercial tab results</t>
-  </si>
-  <si>
-    <t>Tab: Commercial
-Results: First 20 listing cards</t>
-  </si>
-  <si>
-    <t>Zero residential listings appear. Only commercial property types (Office, Shop, Showroom, Warehouse, Industrial) displayed. Any residential listing is a P1 filter contamination defect.</t>
-  </si>
-  <si>
     <t>Test Scenario ID</t>
   </si>
   <si>
     <t>No of Test Cases</t>
   </si>
   <si>
-    <t xml:space="preserve">  Story 1 — Popular Choices</t>
-  </si>
-  <si>
     <t>TS-001</t>
   </si>
   <si>
     <t>Functional</t>
   </si>
   <si>
-    <t>[POSITIVE — TC TC-001]
+    <t>TS-002</t>
+  </si>
+  <si>
+    <t>TS-003</t>
+  </si>
+  <si>
+    <t>TS-004</t>
+  </si>
+  <si>
+    <t>TS-005</t>
+  </si>
+  <si>
+    <t>TS-006</t>
+  </si>
+  <si>
+    <t>TS-007</t>
+  </si>
+  <si>
+    <t>TS-008</t>
+  </si>
+  <si>
+    <t>TS-009</t>
+  </si>
+  <si>
+    <t>TS-010</t>
+  </si>
+  <si>
+    <t>TS-011</t>
+  </si>
+  <si>
+    <t>TS-012</t>
+  </si>
+  <si>
+    <t>TS-013</t>
+  </si>
+  <si>
+    <t>TS-014</t>
+  </si>
+  <si>
+    <t>TS-015</t>
+  </si>
+  <si>
+    <t>TS-016</t>
+  </si>
+  <si>
+    <t>As a homebuyer, I want to filter properties by 'Ready to Move' status so that I can find only those with immediate possession and avoid under-construction delays</t>
+  </si>
+  <si>
+    <t>As a homebuyer, I want to browse properties listed directly by owners so that I can contact them without any broker involvement and save on brokerage fees</t>
+  </si>
+  <si>
+    <t>As a budget-conscious buyer, I want to explore affordable homes within a set price ceiling and use an EMI calculator so that I can assess my repayment capacity before making a decision</t>
+  </si>
+  <si>
+    <t>As a premium property seeker, I want to discover luxury-tier listings with high-quality image galleries so that I can evaluate premium homes in detail before scheduling a site visit</t>
+  </si>
+  <si>
+    <t>As an investor or first-time buyer, I want to explore newly launched projects with RERA compliance details and submit enquiries so that I can track verified projects and connect with builders early</t>
+  </si>
+  <si>
+    <t>As a homebuyer in Mumbai, I want to search specifically for flats and apartments and apply combined BHK and budget filters so that I can quickly shortlist options that match my exact requirements</t>
+  </si>
+  <si>
+    <t>As a homebuyer in Mumbai, I want to browse independent houses and use a Map View to visualise property locations so that I can assess neighbourhood fit and proximity to key areas</t>
+  </si>
+  <si>
+    <t>As a luxury property buyer in Mumbai, I want to explore villa listings with detailed specifications such as plot area, garden, and parking so that I can evaluate the property thoroughly before enquiring</t>
+  </si>
+  <si>
+    <t>As a land investor in Mumbai, I want to search for plots with area-based filters and view dimension details so that I can identify land parcels that meet my investment size requirements</t>
+  </si>
+  <si>
+    <t>As a business owner, I want to browse office spaces in Mumbai with commercial-specific filters and submit enquiries so that I can find a workspace that fits my operational needs</t>
+  </si>
+  <si>
+    <t>As a commercial property buyer, I want to filter commercial spaces in Mumbai by sub-type and sort by price so that I can compare options efficiently across multiple pages</t>
+  </si>
+  <si>
+    <t>SS-01  ·  Story 1: Popular Choices  ·  Verify 'Ready to Move' filter loads results showing only properties with immediate possession</t>
+  </si>
+  <si>
+    <t>SS-02  ·  Story 1: Popular Choices  ·  Verify Owner Properties displays only owner-listed properties and phone reveal requires authentication</t>
+  </si>
+  <si>
+    <t>SS-03  ·  Story 1: Popular Choices  ·  Verify Budget Homes enforces price ceiling and EMI Calculator computes correctly</t>
+  </si>
+  <si>
+    <t>SS-04  ·  Story 1: Popular Choices  ·  Verify Premium Homes shows only luxury-tier listings and image gallery navigation functions correctly</t>
+  </si>
+  <si>
+    <t>SS-05  ·  Story 1: Popular Choices  ·  Verify New Projects cards show mandatory fields and enquiry form validates mobile number before submission</t>
+  </si>
+  <si>
+    <t>SS-06  ·  Story 2: Property Types  ·  Verify Flats in Mumbai results contain only Flat/Apartment type listings and BHK + budget filters combine correctly</t>
+  </si>
+  <si>
+    <t>SS-07  ·  Story 2: Property Types  ·  Verify House for Sale in Mumbai shows only independent dwellings and Map View renders property pins correctly</t>
+  </si>
+  <si>
+    <t>SS-08  ·  Story 2: Property Types  ·  Verify Villa in Mumbai results show only villa-type listings with villa-specific detail fields</t>
+  </si>
+  <si>
+    <t>SS-09  ·  Story 2: Property Types  ·  Verify Plot in Mumbai has no BHK filter and detail pages display plot-specific fields including dimensions and zone type</t>
+  </si>
+  <si>
+    <t>URL manipulation: &amp;bhk=2 added to Plot results URL
+Browser: Chrome latest</t>
+  </si>
+  <si>
+    <t>SS-10  ·  Story 2: Property Types  ·  Verify Office Space in Mumbai shows only commercial listings with commercial-specific filters and validates enquiry form</t>
+  </si>
+  <si>
+    <t>SS-11  ·  Story 2: Property Types  ·  Verify Commercial Space in Mumbai supports sub-type filtering and sort order persists across pagination</t>
+  </si>
+  <si>
+    <t>SS-12  ·  Story 3: Search Bar  ·  Verify Buy tab in search bar is active by default with correct sale filters and restores correctly after tab switch</t>
+  </si>
+  <si>
+    <t>SS-13  ·  Story 3: Search Bar  ·  Verify Rent tab switches context to rental listings with updated URL param and rent-specific Budget filter label</t>
+  </si>
+  <si>
+    <t>SS-14  ·  Story 3: Search Bar  ·  Verify PG tab shows PG-specific filters including Gender Preference and hides BHK and Property Type filters</t>
+  </si>
+  <si>
+    <t>SS-15  ·  Story 3: Search Bar  ·  Verify Plot tab shows area-based filters, excludes BHK filter, and returns only Plot/Land type listings</t>
+  </si>
+  <si>
+    <t>SS-16  ·  Story 3: Search Bar  ·  Verify Commercial tab shows Rent/Lease sub-options with Office Space Type filter and returns only commercial listings</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-001]
 Steps:
 1. Open magicbricks.com
 2. Hover over 'Buy' in top navigation
 3. Click 'Ready to Move' under Popular Choices
 4. Observe results page and inspect possession tag on 5 listing cards
 Expected Result:
-Results page loads with 'Ready to Move' filter chip active. All 5 inspected cards show 'Ready to Move' possession tag. URL reflects possession filter param.
-────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-002]
-Steps:
-1. Navigate to Ready to Move results page
-2. Scroll through all visible listing cards on page 1
-3. Look specifically for any card showing 'Under Construction' or a future possession date
-Expected Result:
-Zero Under Construction or future-possession listings appear. Filter is strictly enforced. Any such listing found is a P1 data integrity defect.</t>
-  </si>
-  <si>
-    <t>TS-002</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-003]
+Results page loads with 'Ready to Move' filter chip active. All 5 inspected cards show 'Ready to Move' possession tag. URL reflects possession filter param.</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-002]
 Steps:
 1. Log in to MagicBricks with valid credentials
 2. Hover 'Buy' &gt; click 'Owner Properties'
 3. Inspect badge on first 5 listing cards
 4. Open a listing and click 'View Phone Number'
 Expected Result:
-All 5 cards display 'Owner' badge. Phone number is revealed in full after clicking. Contact event is logged under My Enquiries in the user's profile.
+All 5 cards display 'Owner' badge. Phone number is revealed in full after clicking. Contact event is logged under My Enquiries.
 ────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-004]
+[NEGATIVE — TC-003]
 Steps:
 1. Ensure you are NOT logged in (use incognito window)
 2. Navigate to Owner Properties results
@@ -1304,10 +1166,7 @@
 Login/signup modal appears when 'View Phone Number' is clicked. Phone number is NOT revealed. Zero Broker or Agent tagged listings appear in results.</t>
   </si>
   <si>
-    <t>TS-003</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-005]
+    <t>[POSITIVE — TC-004]
 Steps:
 1. Hover 'Buy' &gt; click 'Budget Homes'
 2. Note the price filter chip value on results page
@@ -1316,7 +1175,7 @@
 Expected Result:
 All 5 listing card prices are within the budget ceiling. EMI Calculator displays approximately ₹26,035 (±₹50). Result appears without page reload.
 ────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-006]
+[NEGATIVE — TC-005]
 Steps:
 1. Open EMI Calculator on any Budget Homes listing
 2. Clear the loan amount field and enter '0'
@@ -1326,31 +1185,17 @@
 Entering 0 in loan amount shows validation error 'Enter a valid loan amount greater than 0'. Alphabetic input in interest rate field is rejected. No EMI value calculated. No NaN or error code displayed.</t>
   </si>
   <si>
-    <t>TS-004</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-007]
+    <t>[POSITIVE — TC-006]
 Steps:
 1. Hover 'Buy' &gt; click 'Premium Homes'
 2. Check prices of first 3 listing cards
 3. Open a listing detail page &gt; click through gallery using next arrow 3 times
 4. Note image counter value
 Expected Result:
-All 3 cards priced above the luxury threshold. Gallery cycles correctly with each next click. Counter updates accurately (e.g. 1/10 → 2/10 → 3/10 → 4/10). High-res images load within 3 seconds.
-────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-008]
-Steps:
-1. Navigate to Premium Homes results
-2. Look for any listing priced below ₹50L or tagged 'Budget' or 'Affordable'
-3. Also open a listing that has only 1 image and attempt to click the next arrow
-Expected Result:
-Zero budget-segment listings found in Premium Homes results. On a single-image listing, the next/prev arrows are hidden or disabled. Counter shows '1/1'. No JS error thrown.</t>
-  </si>
-  <si>
-    <t>TS-005</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-009]
+All 3 cards priced above the luxury threshold. Gallery cycles correctly with each next click. Counter updates accurately (e.g. 1/10 → 2/10 → 3/10 → 4/10). High-res images load within 3 seconds.</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-007]
 Steps:
 1. Hover 'Buy' &gt; click 'New Projects'
 2. Inspect 3 project cards for required fields
@@ -1360,7 +1205,7 @@
 Expected Result:
 Each card shows project name, builder name, RERA number, launch date, and starting price. Enquiry submitted successfully. Confirmation message shown. Lead visible in My Enquiries.
 ────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-010]
+[NEGATIVE — TC-008]
 Steps:
 1. Open any New Project enquiry form
 2. Fill Name and Message fields only
@@ -1370,75 +1215,36 @@
 Form submission is blocked. Validation error 'Mobile number is required' appears adjacent to the phone field. Field highlighted in error state. No lead is sent to the builder.</t>
   </si>
   <si>
-    <t xml:space="preserve">  Story 2 — Property Types</t>
-  </si>
-  <si>
-    <t>TS-006</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-011]
+    <t>[POSITIVE — TC-009]
 Steps:
 1. Hover 'Buy' &gt; click 'Flats in Mumbai' under Property Types
 2. Check page heading and property type on first 5 cards
 3. Select '2 BHK' filter + set budget ₹50L–₹1Cr
 4. Click Apply and review results
 Expected Result:
-Page heading reads 'Flats for Sale in Mumbai'. All 5 cards are Flat/Apartment type. After applying filters, results show only 2 BHK flats priced between ₹50L–₹1Cr. Both filter chips are active.
-────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-012]
-Steps:
-1. Navigate to Flats in Mumbai results
-2. Scan first 20 listing cards
-3. Look for any Villa, Plot, Office, or Commercial property type listing
-Expected Result:
-Zero non-flat property types appear in the results. Villa, Plot, and Commercial listings are completely absent. Filter is strictly enforced across all visible results.</t>
-  </si>
-  <si>
-    <t>TS-007</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-013]
+Page heading reads 'Flats for Sale in Mumbai'. All 5 cards are Flat/Apartment type. After applying filters, results show only 2 BHK flats priced between ₹50L–₹1Cr. Both filter chips are active.</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-010]
 Steps:
 1. Hover 'Buy' &gt; click 'House for Sale in Mumbai'
 2. Check property type on first 5 cards
 3. Click 'Map View' toggle
 4. Click on any property pin on the map
 Expected Result:
-All 5 cards show Independent House / Builder Floor type. Map loads within 3 seconds with pins at correct Mumbai coordinates. Clicking a pin shows a mini-card popup with image, price, area, and 'View Details' CTA.
-────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-014]
-Steps:
-1. Apply filters on House for Sale results that yield zero listings
-2. Switch to Map View
-3. Observe the map state and messaging
-Expected Result:
-Map tiles render correctly showing Mumbai map. Empty state message is overlaid: 'No properties to show for current filters'. No JavaScript error. No blank white canvas.</t>
-  </si>
-  <si>
-    <t>TS-008</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-015]
+All 5 cards show Independent House / Builder Floor type. Map loads within 3 seconds with pins at correct Mumbai coordinates. Clicking a pin shows a mini-card popup with image, price, area, and 'View Details' CTA.</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-011]
 Steps:
 1. Hover 'Buy' &gt; click 'Villa in Mumbai'
 2. Open 2 villa listing detail pages
 3. Check property specification section on each
 Expected Result:
-Results show only Villa type listings. Both detail pages display villa-specific fields: plot area, number of floors, facing direction, private garden (Yes/No), and number of car parks.
-────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-016]
-Steps:
-1. Navigate to Villa in Mumbai results
-2. Scan for any Studio Apartment, 1 RK, or Flat listing
-3. Also open a Villa listing where seller has NOT uploaded a floor plan &gt; click Floor Plan tab
-Expected Result:
-Zero flat or apartment listings present in results. Floor Plan tab on the listing without upload shows 'Floor plan not available for this property'. No broken image icon or blank space.</t>
-  </si>
-  <si>
-    <t>TS-009</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-017]
+Results show only Villa type listings. Both detail pages display villa-specific fields: plot area, number of floors, facing direction, private garden (Yes/No), and number of car parks.</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-012]
 Steps:
 1. Hover 'Buy' &gt; click 'Plot in Mumbai'
 2. Check the filter panel for BHK filter
@@ -1447,7 +1253,7 @@
 Expected Result:
 BHK filter is completely absent from the filter panel. Area filter narrows results to plots between 500–1000 sq yards. Detail page shows plot area, dimensions (L×B), facing direction, zone type, and price per sq ft.
 ────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-018]
+[NEGATIVE — TC-013]
 Steps:
 1. Navigate to Plot in Mumbai results
 2. Manually edit the URL to add a BHK param (e.g. &amp;bhk=2)
@@ -1456,10 +1262,7 @@
 No built-up or apartment-type properties appear. System either ignores the BHK URL param for plot results or returns 0 results with a message. Plot-only filter is not overridden by URL manipulation.</t>
   </si>
   <si>
-    <t>TS-010</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-019]
+    <t>[POSITIVE — TC-014]
 Steps:
 1. Hover 'Buy' &gt; click 'Office Space in Mumbai'
 2. Check filter panel for BHK filter presence
@@ -1468,7 +1271,7 @@
 Expected Result:
 BHK filter is absent. Commercial filters present (carpet area, furnishing status, floor number). All 5 cards are Office Space type. Enquiry submitted successfully with confirmation toast shown.
 ────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-020]
+[NEGATIVE — TC-015]
 Steps:
 1. Open an Office Space listing enquiry form
 2. Enter phone number as '987654' (only 6 digits)
@@ -1477,56 +1280,27 @@
 Form is not submitted. Field-level validation error 'Please enter a valid 10-digit mobile number' appears. Phone field is highlighted with error styling. No lead is created in the system.</t>
   </si>
   <si>
-    <t>TS-011</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-021]
+    <t>[POSITIVE — TC-016]
 Steps:
 1. Hover 'Buy' &gt; click 'Commercial Space in Mumbai'
 2. Select sub-type filter 'Shop'
 3. Apply sort 'Price: High to Low'
 4. Navigate to page 2 and check first listing price vs last listing on page 1
 Expected Result:
-Only Shop sub-type listings shown after filter applied. Results on page 1 are in descending price order. Page 2 loads the next batch with prices lower than page 1's last listing. Sort and filter chips remain active.
-────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-022]
-Steps:
-1. On Commercial Space results page
-2. Manually edit URL to set page=9999
-3. Load the page and observe the response
-Expected Result:
-Page displays the last valid page OR a clean empty state 'No more results'. No HTTP 500 server error. Navigation controls (Previous, First page) still function correctly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Story 3 — Search Bar Tabs</t>
-  </si>
-  <si>
-    <t>TS-012</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-023]
+Only Shop sub-type listings shown after filter applied. Results on page 1 are in descending price order. Page 2 loads the next batch with prices lower than page 1's last listing. Sort and filter chips remain active.</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-017]
 Steps:
 1. Open the MagicBricks residential results page
 2. Observe which tab is active in the search bar
 3. Click the Rent tab, then click Buy tab again
 4. Check URL param and active filters
 Expected Result:
-Buy tab is highlighted/active on page load. category=S present in URL. After switching Rent → Buy, category returns to S and sale listings reload. Filters shown: Location, Property Type, Budget Min–Max.
-────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-024]
-Steps:
-1. Open the results page with category=S in URL
-2. Do NOT click any tab
-3. Press F5 to hard refresh the page
-4. Check which tab is active after refresh
-Expected Result:
-After refresh, Buy tab remains active and category=S is preserved in the URL. Results still show sale listings. No accidental switch to Rent or any other tab occurs on page reload.</t>
-  </si>
-  <si>
-    <t>TS-013</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-025]
+Buy tab is highlighted/active on page load. category=S present in URL. After switching Rent → Buy, category returns to S and sale listings reload. Filters shown: Location, Property Type, Budget Min–Max.</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-018]
 Steps:
 1. Click the 'Rent' tab in the search bar
 2. Observe URL param change
@@ -1534,44 +1308,20 @@
 4. Check Budget filter label
 5. Inspect 3 listing cards
 Expected Result:
-URL param changes to category=R. Page heading updates to 'Properties for Rent in [City]'. Budget filter label reads 'Rent/Month'. All 3 inspected cards show monthly rent price, not sale price.
-────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-026]
-Steps:
-1. Enter location 'Gachibowli' in the Location filter
-2. Set a budget range under the Buy tab
-3. Switch to Rent tab
-4. Observe the location field and budget field values
-Expected Result:
-Location 'Gachibowli' is retained after switching to Rent tab. Budget range is reset (rent ranges differ from sale prices). No stale sale budget value carried over to Rent context.</t>
-  </si>
-  <si>
-    <t>TS-014</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-027]
+URL param changes to category=R. Page heading updates to 'Properties for Rent in [City]'. Budget filter label reads 'Rent/Month'. All 3 inspected cards show monthly rent price, not sale price.</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-019]
 Steps:
 1. Click the 'PG' tab in the search bar
 2. Check available filters in the search bar
 3. Enter a location and execute a PG search
 4. Inspect 3 result cards
 Expected Result:
-Filter panel shows: Location, Gender Preference (Male/Female/Co-ed), Monthly Rent range. BHK and Property Type filters are completely absent. All 3 result cards show PG/co-living type accommodations.
-────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-028]
-Steps:
-1. Click the PG tab
-2. Select a city/locality where no PG listings exist
-3. Execute the search
-4. Observe the results page
-Expected Result:
-Empty state displayed: 'No PG accommodations found in [Location]'. Suggestion to try a nearby area or different location shown. No blank page or broken layout. Search bar remains accessible for a new search.</t>
-  </si>
-  <si>
-    <t>TS-015</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-029]
+Filter panel shows: Location, Gender Preference (Male/Female/Co-ed), Monthly Rent range. BHK and Property Type filters are completely absent. All 3 result cards show PG/co-living type accommodations.</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-020]
 Steps:
 1. Click the 'Plot' tab in the search bar
 2. Check the filter panel for available filters
@@ -1580,7 +1330,7 @@
 Expected Result:
 Filter panel shows: Location, Plot Area (sq yards Min–Max), Budget (Min–Max). BHK filter is completely absent. All 5 result cards show Plot/Land type only. Area filter correctly narrows results.
 ────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-030]
+[NEGATIVE — TC-021]
 Steps:
 1. Click the Plot tab in the search bar
 2. Enter Plot Area Min as '2000' and Max as '500' (Min greater than Max)
@@ -1589,10 +1339,7 @@
 Search is not executed. Validation error shown: 'Minimum area cannot be greater than maximum area'. Fields highlighted in error state. No results loaded with the inverted range.</t>
   </si>
   <si>
-    <t>TS-016</t>
-  </si>
-  <si>
-    <t>[POSITIVE — TC TC-031]
+    <t>[POSITIVE — TC-022]
 Steps:
 1. Click the 'Commercial' tab in the search bar
 2. Check for Rent and Lease sub-options
@@ -1600,15 +1347,238 @@
 4. Select Office Space Type = 'Warehouse'
 5. Click Search and check 5 result cards
 Expected Result:
-Rent and Lease sub-options are visible. Office Space Type filter shows options: Office Space, Shop, Showroom, Warehouse, Co-working Space. After selecting Warehouse, all 5 result cards show Warehouse type only.
+Rent and Lease sub-options are visible. Office Space Type filter shows options: Office Space, Shop, Showroom, Warehouse, Co-working Space. After selecting Warehouse, all 5 result cards show Warehouse type only.</t>
+  </si>
+  <si>
+    <t>Epic 2</t>
+  </si>
+  <si>
+    <t>End-to-End Functional Validation of Post Property Feature on MagicBricks Website</t>
+  </si>
+  <si>
+    <t>Story 4</t>
+  </si>
+  <si>
+    <t>As a property owner or broker, I want to post my property for sale or rent on MagicBricks so that I can reach a large pool of potential buyers or tenants quickly.</t>
+  </si>
+  <si>
+    <t>Sub Story 17</t>
+  </si>
+  <si>
+    <t>As a property owner, I want to fill in the basic property details (type, city, locality, and listing type) so that my property is correctly categorised and visible to the right audience.</t>
+  </si>
+  <si>
+    <t>Sub Story 18</t>
+  </si>
+  <si>
+    <t>As a property owner, I want to provide property specifications such as BHK type, built-up area, floor details, and amenities so that prospective buyers have all the information needed to make an enquiry.</t>
+  </si>
+  <si>
+    <t>Sub Story 19</t>
+  </si>
+  <si>
+    <t>As a property owner, I want to set a pricing, add photos, and submit my listing so that my property is live on MagicBricks and enquiries start coming in from interested buyers or tenants.</t>
+  </si>
+  <si>
+    <t>TS-017</t>
+  </si>
+  <si>
+    <t>SS-17</t>
+  </si>
+  <si>
+    <t>Verify that the Post Property form loads correctly and allows a user to select property type, listing type (Sale/Rent), city, and locality without errors</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-023]
+Steps:
+1. Open https://post.magicbricks.com/postproperty/post-property-for-sale-rent/residential-commercial
+2. Select Property Type = 'Residential' &gt; 'Apartment'
+3. Select Listing Type = 'Sale'
+4. Enter City = 'Mumbai' and Locality = 'Andheri West'
+5. Click 'Next'
+Expected Result:
+Form loads without errors. All dropdowns and fields are functional. On clicking Next, the user is taken to the property specifications step. Selected values (Apartment, Sale, Mumbai, Andheri West) are retained and displayed.</t>
+  </si>
+  <si>
+    <t>TS-018</t>
+  </si>
+  <si>
+    <t>SS-18</t>
+  </si>
+  <si>
+    <t>Verify that the property specifications step captures BHK type, built-up area, floor details, and amenities, and that mandatory fields enforce validation on empty submission</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-024]
+Steps:
+1. Reach the Property Specifications step (after completing Step 1)
+2. Select BHK = '2 BHK', Built-up Area = '950 sq ft'
+3. Select Total Floors = '10', Property on Floor = '5'
+4. Select amenities: Lift, Parking, Power Backup
+5. Click 'Next'
+Expected Result:
+All fields accept valid inputs. On clicking Next, user proceeds to the pricing &amp; photos step. Selected specifications (2 BHK, 950 sq ft, Floor 5/10, amenities) are retained in the summary panel.
 ────────────────────────────────────────────────────────────
-[NEGATIVE — TC TC-032]
+[NEGATIVE — TC-025]
 Steps:
-1. Navigate to Commercial tab results
-2. Carefully scan first 20 listing cards
-3. Look for any Flat, House, Villa, or Plot listing
+1. Reach the Property Specifications step
+2. Leave BHK type and Built-up Area fields completely blank
+3. Click 'Next' without filling any mandatory field
 Expected Result:
-Zero residential listings appear in Commercial tab results. Only commercial property types (Office, Shop, Showroom, Warehouse, Industrial) are displayed. Any residential listing is a P1 filter contamination defect.</t>
+Form submission is blocked. Validation errors appear: 'BHK type is required' and 'Built-up area is required' adjacent to the respective fields. Fields are highlighted in error state. User remains on the same step.</t>
+  </si>
+  <si>
+    <t>TS-019</t>
+  </si>
+  <si>
+    <t>SS-19</t>
+  </si>
+  <si>
+    <t>Verify that a property owner can set a price, upload photos, and successfully submit the listing, and that submission without a price is blocked with a validation error</t>
+  </si>
+  <si>
+    <t>[POSITIVE — TC-026]
+Steps:
+1. Reach the Pricing &amp; Photos step
+2. Enter Expected Price = ₹85,00,000
+3. Upload 3 property photos (JPG, each &lt; 5 MB)
+4. Enter Owner Name = 'Rajesh Kumar', Mobile = 9876543210
+5. Click 'Post Property'
+Expected Result:
+Photos upload successfully with progress indicators. On clicking Post Property, a confirmation screen is shown: 'Your property has been posted successfully'. A listing ID is generated. The listing is visible under 'My Properties' in the owner dashboard.
+────────────────────────────────────────────────────────────
+[NEGATIVE — TC-027]
+Steps:
+1. Reach the Pricing &amp; Photos step
+2. Leave the Expected Price field completely blank
+3. Upload photos and fill in owner contact details
+4. Click 'Post Property'
+Expected Result:
+Submission is blocked. Validation error 'Expected price is required' appears adjacent to the price field. Field is highlighted in error state. No listing is created. User remains on the Pricing &amp; Photos step.</t>
+  </si>
+  <si>
+    <t>SS-17  ·  Story 4: Post Property  ·  Verify Post Property form loads correctly and allows selection of property type, listing type, city and locality</t>
+  </si>
+  <si>
+    <t>Verify Post Property form loads correctly and allows selection of property type, listing type, city and locality</t>
+  </si>
+  <si>
+    <t>User has a valid MagicBricks account and is logged in. The Post Property URL is accessible: https://post.magicbricks.com/postproperty/post-property-for-sale-rent/residential-commercial</t>
+  </si>
+  <si>
+    <t>All dropdowns and fields must be functional and values retained when user proceeds to the next step</t>
+  </si>
+  <si>
+    <t>1. Open the Post Property URL
+2. Select Property Type = 'Residential' &gt; 'Apartment'
+3. Select Listing Type = 'Sale'
+4. Enter City = 'Mumbai' and Locality = 'Andheri West'
+5. Click 'Next'</t>
+  </si>
+  <si>
+    <t>URL: post.magicbricks.com/postproperty/...
+Property Type: Apartment
+Listing Type: Sale
+City: Mumbai
+Locality: Andheri West</t>
+  </si>
+  <si>
+    <t>Form loads without errors. All fields are interactive. On clicking Next, user proceeds to specifications step. Selected values (Apartment, Sale, Mumbai, Andheri West) are retained and shown in the step summary.</t>
+  </si>
+  <si>
+    <t>SS-18  ·  Story 4: Post Property  ·  Verify property specifications step captures BHK, area, floor details and validates mandatory fields</t>
+  </si>
+  <si>
+    <t>Verify property specifications step captures BHK type, built-up area, floor details and amenities correctly</t>
+  </si>
+  <si>
+    <t>User has completed Step 1 (basic details) and is on the Property Specifications step.</t>
+  </si>
+  <si>
+    <t>All specification fields must accept valid inputs and user must be able to proceed to the next step</t>
+  </si>
+  <si>
+    <t>1. Reach the Property Specifications step
+2. Select BHK = '2 BHK', Built-up Area = '950 sq ft'
+3. Select Total Floors = '10', Property on Floor = '5'
+4. Select amenities: Lift, Parking, Power Backup
+5. Click 'Next'</t>
+  </si>
+  <si>
+    <t>BHK: 2 BHK
+Built-up Area: 950 sq ft
+Total Floors: 10
+Floor No: 5
+Amenities: Lift, Parking, Power Backup</t>
+  </si>
+  <si>
+    <t>All fields accept valid inputs. On clicking Next, user proceeds to the pricing &amp; photos step. Selected specifications (2 BHK, 950 sq ft, Floor 5/10, amenities) are retained in the step summary panel.</t>
+  </si>
+  <si>
+    <t>Mandatory fields (BHK type and Built-up area) must block progression when left empty</t>
+  </si>
+  <si>
+    <t>1. Reach the Property Specifications step
+2. Leave BHK type field blank
+3. Leave Built-up Area field blank
+4. Click 'Next' without filling any mandatory field</t>
+  </si>
+  <si>
+    <t>BHK: (blank)
+Built-up Area: (blank)</t>
+  </si>
+  <si>
+    <t>Form submission is blocked. Validation errors appear: 'BHK type is required' and 'Built-up area is required' adjacent to respective fields. Fields highlighted in error state. User remains on the same step.</t>
+  </si>
+  <si>
+    <t>SS-19  ·  Story 4: Post Property  ·  Verify pricing, photo upload and final listing submission works correctly and price is mandatory</t>
+  </si>
+  <si>
+    <t>Verify property owner can set price, upload photos and successfully submit the listing</t>
+  </si>
+  <si>
+    <t>User has completed Steps 1 and 2 and is on the Pricing &amp; Photos step. Valid JPG photos under 5 MB are available for upload.</t>
+  </si>
+  <si>
+    <t>A valid price and at least one photo must allow the listing to be submitted successfully</t>
+  </si>
+  <si>
+    <t>1. Reach the Pricing &amp; Photos step
+2. Enter Expected Price = ₹85,00,000
+3. Upload 3 property photos (JPG, each &lt; 5 MB)
+4. Enter Owner Name = 'Rajesh Kumar', Mobile = 9876543210
+5. Click 'Post Property'</t>
+  </si>
+  <si>
+    <t>Expected Price: ₹85,00,000
+Photos: 3 JPG files &lt; 5 MB each
+Owner Name: Rajesh Kumar
+Mobile: 9876543210</t>
+  </si>
+  <si>
+    <t>Photos upload successfully with progress indicators shown. On clicking Post Property, confirmation screen shows: 'Your property has been posted successfully'. A listing ID is generated. Listing is visible under My Properties in the owner dashboard.</t>
+  </si>
+  <si>
+    <t>User has completed Steps 1 and 2 and is on the Pricing &amp; Photos step.</t>
+  </si>
+  <si>
+    <t>Leaving Expected Price field blank must block submission with a validation error</t>
+  </si>
+  <si>
+    <t>1. Reach the Pricing &amp; Photos step
+2. Leave Expected Price field completely blank
+3. Upload at least one photo
+4. Fill in Owner Name and Mobile
+5. Click 'Post Property'</t>
+  </si>
+  <si>
+    <t>Expected Price: (blank)
+Photos: 1 JPG file
+Owner Name: Test Owner
+Mobile: 9876543210</t>
+  </si>
+  <si>
+    <t>Submission is blocked. Validation error 'Expected price is required' appears adjacent to the price field. Field is highlighted in error state. No listing is created. User remains on the Pricing &amp; Photos step.</t>
   </si>
 </sst>
 </file>
@@ -1621,6 +1591,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1689,13 +1666,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1716,33 +1686,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF1565C0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1751,26 +1694,56 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F4E79"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF6A1B9A"/>
+      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF00695C"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="4" tint="-0.499984740745262"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1791,13 +1764,57 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1895,15 +1912,15 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1913,7 +1930,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1926,13 +1943,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1942,70 +1959,119 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2314,247 +2380,303 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27D7147E-2CC2-44FC-9B78-361680BF6B3F}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="33.88671875" customWidth="1"/>
-    <col min="2" max="2" width="39.6640625" customWidth="1"/>
+    <col min="2" max="2" width="72.88671875" customWidth="1"/>
     <col min="3" max="3" width="51.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="32" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="39.6">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="41.4">
+      <c r="A3" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="54" customHeight="1">
+      <c r="A4" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.8">
+      <c r="A5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>305</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="66.599999999999994" customHeight="1">
+      <c r="A6" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>306</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="44.4" customHeight="1">
+      <c r="A7" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="48" customHeight="1">
+      <c r="A8" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="41.4">
+      <c r="A9" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="51" customHeight="1">
+      <c r="A10" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>309</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="68.400000000000006" customHeight="1">
+      <c r="A11" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="B11" s="26" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="66">
-      <c r="A3" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="23" t="s">
+    <row r="12" spans="1:3" ht="52.8" customHeight="1">
+      <c r="A12" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="B12" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="26.4">
-      <c r="A4" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="25" t="s">
+    <row r="13" spans="1:3" ht="52.2" customHeight="1">
+      <c r="A13" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="B13" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="26.4">
-      <c r="A5" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="25" t="s">
+    <row r="14" spans="1:3" ht="49.8" customHeight="1">
+      <c r="A14" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="B14" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="26.4">
-      <c r="A6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="25" t="s">
+    <row r="15" spans="1:3" ht="60.6" customHeight="1">
+      <c r="A15" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="B15" s="26" t="s">
+        <v>314</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="26.4">
-      <c r="A7" s="24" t="s">
+    <row r="16" spans="1:3" ht="27.6">
+      <c r="A16" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="C16" s="21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="27.6">
+      <c r="A17" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="B17" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="27.6">
+      <c r="A18" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="27.6">
+      <c r="A19" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27.6">
+      <c r="A20" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="26.4">
-      <c r="A8" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="C8" s="22" t="s">
+    <row r="21" spans="1:3" ht="49.8" customHeight="1">
+      <c r="A21" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="66">
-      <c r="A9" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="22" t="s">
+    <row r="22" spans="1:3">
+      <c r="A22" s="49" t="s">
+        <v>348</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>349</v>
+      </c>
+      <c r="C22" s="49" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="26.4">
-      <c r="A10" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="22" t="s">
+    <row r="23" spans="1:3" ht="27.6">
+      <c r="A23" s="51" t="s">
+        <v>350</v>
+      </c>
+      <c r="B23" s="52" t="s">
+        <v>351</v>
+      </c>
+      <c r="C23" s="51" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="39.6">
-      <c r="A11" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="22" t="s">
+    <row r="24" spans="1:3" ht="43.2">
+      <c r="A24" s="53" t="s">
+        <v>352</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="C24" s="54" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="26.4">
-      <c r="A12" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" s="22" t="s">
+    <row r="25" spans="1:3" ht="43.2">
+      <c r="A25" s="53" t="s">
+        <v>354</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>355</v>
+      </c>
+      <c r="C25" s="54" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="26.4">
-      <c r="A13" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="39.6">
-      <c r="A14" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="26.4">
-      <c r="A15" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="66">
-      <c r="A16" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="39.6">
-      <c r="A17" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="39.6">
-      <c r="A18" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="52.8">
-      <c r="A19" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="39.6">
-      <c r="A20" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="129.6" customHeight="1">
-      <c r="A21" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="C21" s="22" t="s">
+    <row r="26" spans="1:3" ht="43.2">
+      <c r="A26" s="53" t="s">
+        <v>356</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>357</v>
+      </c>
+      <c r="C26" s="54" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2565,380 +2687,410 @@
   <cols>
     <col min="1" max="1" width="28.33203125" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" customWidth="1"/>
-    <col min="3" max="3" width="31.88671875" customWidth="1"/>
-    <col min="4" max="4" width="27.44140625" customWidth="1"/>
-    <col min="5" max="5" width="33.5546875" customWidth="1"/>
-    <col min="6" max="6" width="26.21875" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="77.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:6" ht="82.8" customHeight="1">
+      <c r="A1" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="151.80000000000001" customHeight="1">
+      <c r="A2" s="55" t="s">
+        <v>287</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E2" s="34">
+        <v>1</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="256.2" customHeight="1">
+      <c r="A3" s="55" t="s">
+        <v>289</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E3" s="34">
+        <v>2</v>
+      </c>
+      <c r="F3" s="35" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="117" customHeight="1">
+      <c r="A4" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E4" s="34">
+        <v>2</v>
+      </c>
+      <c r="F4" s="35" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="54.6" customHeight="1">
+      <c r="A5" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E5" s="34">
+        <v>1</v>
+      </c>
+      <c r="F5" s="35" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="79.2" customHeight="1">
+      <c r="A6" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E6" s="34">
+        <v>2</v>
+      </c>
+      <c r="F6" s="35" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="87" customHeight="1">
+      <c r="A7" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="34">
+        <v>1</v>
+      </c>
+      <c r="F7" s="35" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="67.8" customHeight="1">
+      <c r="A8" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E8" s="34">
+        <v>1</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="84" customHeight="1">
+      <c r="A9" s="55" t="s">
+        <v>295</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E9" s="34">
+        <v>1</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="82.2" customHeight="1">
+      <c r="A10" s="55" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E10" s="34">
+        <v>2</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="85.2" customHeight="1">
+      <c r="A11" s="55" t="s">
+        <v>297</v>
+      </c>
+      <c r="B11" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E11" s="34">
+        <v>2</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="88.2" customHeight="1">
+      <c r="A12" s="55" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E12" s="34">
+        <v>1</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="99.6" customHeight="1">
+      <c r="A13" s="55" t="s">
+        <v>299</v>
+      </c>
+      <c r="B13" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E13" s="34">
+        <v>1</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="94.2" customHeight="1">
+      <c r="A14" s="55" t="s">
+        <v>300</v>
+      </c>
+      <c r="B14" s="55" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E14" s="34">
+        <v>1</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="61.8" customHeight="1">
+      <c r="A15" s="55" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E15" s="34">
+        <v>1</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="95.4" hidden="1" customHeight="1">
+      <c r="A16" s="55" t="s">
+        <v>302</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E16" s="34">
+        <v>2</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="91.8" customHeight="1">
+      <c r="A17" s="55" t="s">
+        <v>303</v>
+      </c>
+      <c r="B17" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E17" s="34">
+        <v>1</v>
+      </c>
+      <c r="F17" s="35" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="72" customHeight="1">
+      <c r="A18" s="55" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="32" t="s">
+      <c r="B18" s="55" t="s">
         <v>359</v>
       </c>
-      <c r="F1" s="32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="14.4" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="C18" s="35" t="s">
         <v>360</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-    </row>
-    <row r="3" spans="1:6" ht="71.400000000000006" customHeight="1">
-      <c r="A3" s="35" t="s">
+      <c r="D18" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E18" s="34">
+        <v>1</v>
+      </c>
+      <c r="F18" s="35" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="D3" s="37" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="94.8" customHeight="1">
+      <c r="A19" s="55" t="s">
         <v>362</v>
       </c>
-      <c r="E3" s="38">
+      <c r="B19" s="55" t="s">
+        <v>363</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>364</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" s="34">
         <v>2</v>
       </c>
-      <c r="F3" s="39" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="117" customHeight="1">
-      <c r="A4" s="35" t="s">
-        <v>364</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E4" s="38">
+      <c r="F19" s="35" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="99.6" customHeight="1">
+      <c r="A20" s="55" t="s">
+        <v>366</v>
+      </c>
+      <c r="B20" s="55" t="s">
+        <v>367</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>368</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="E20" s="34">
         <v>2</v>
       </c>
-      <c r="F4" s="39" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="54.6" customHeight="1">
-      <c r="A5" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E5" s="38">
-        <v>2</v>
-      </c>
-      <c r="F5" s="39" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="79.2" customHeight="1">
-      <c r="A6" s="35" t="s">
-        <v>368</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E6" s="38">
-        <v>2</v>
-      </c>
-      <c r="F6" s="39" t="s">
+      <c r="F20" s="35" t="s">
         <v>369</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="87" customHeight="1">
-      <c r="A7" s="35" t="s">
-        <v>370</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E7" s="38">
-        <v>2</v>
-      </c>
-      <c r="F7" s="39" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.4" customHeight="1">
-      <c r="A8" s="33" t="s">
-        <v>372</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-    </row>
-    <row r="9" spans="1:6" ht="84" customHeight="1">
-      <c r="A9" s="40" t="s">
-        <v>373</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E9" s="38">
-        <v>2</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="82.2" customHeight="1">
-      <c r="A10" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="B10" s="40" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E10" s="38">
-        <v>2</v>
-      </c>
-      <c r="F10" s="39" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.4" customHeight="1">
-      <c r="A11" s="40" t="s">
-        <v>377</v>
-      </c>
-      <c r="B11" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E11" s="38">
-        <v>2</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="88.2" customHeight="1">
-      <c r="A12" s="40" t="s">
-        <v>379</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="36" t="s">
-        <v>118</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E12" s="38">
-        <v>2</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="99.6" customHeight="1">
-      <c r="A13" s="40" t="s">
-        <v>381</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="D13" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E13" s="38">
-        <v>2</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="14.4" customHeight="1">
-      <c r="A14" s="40" t="s">
-        <v>383</v>
-      </c>
-      <c r="B14" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E14" s="38">
-        <v>2</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="61.8" customHeight="1">
-      <c r="A15" s="33" t="s">
-        <v>385</v>
-      </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-    </row>
-    <row r="16" spans="1:6" ht="95.4" hidden="1" customHeight="1">
-      <c r="A16" s="41" t="s">
-        <v>386</v>
-      </c>
-      <c r="B16" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="D16" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E16" s="38">
-        <v>2</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="14.4" customHeight="1">
-      <c r="A17" s="41" t="s">
-        <v>388</v>
-      </c>
-      <c r="B17" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="D17" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E17" s="38">
-        <v>2</v>
-      </c>
-      <c r="F17" s="39" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="72" customHeight="1">
-      <c r="A18" s="41" t="s">
-        <v>390</v>
-      </c>
-      <c r="B18" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D18" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E18" s="38">
-        <v>2</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="43.8" customHeight="1">
-      <c r="A19" s="41" t="s">
-        <v>392</v>
-      </c>
-      <c r="B19" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E19" s="38">
-        <v>2</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="14.4" customHeight="1">
-      <c r="A20" s="41" t="s">
-        <v>394</v>
-      </c>
-      <c r="B20" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>362</v>
-      </c>
-      <c r="E20" s="38">
-        <v>2</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="89.4" customHeight="1"/>
@@ -2971,18 +3123,13 @@
     <row r="48" ht="83.4" customHeight="1"/>
     <row r="49" ht="66.599999999999994" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A8:F8"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C39145A-3C54-4038-8F33-5414E910824C}">
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -2995,1329 +3142,1207 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="84">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="K1" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="L1" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="72">
+      <c r="A2" s="38" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+    </row>
+    <row r="3" spans="1:13" ht="118.8">
+      <c r="A3" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>175</v>
+      </c>
+      <c r="H3" s="41"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="40" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="72">
+      <c r="A4" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+    </row>
+    <row r="5" spans="1:13" ht="118.8">
+      <c r="A5" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="H5" s="43"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="118.8">
+      <c r="A6" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="E6" s="46" t="s">
         <v>183</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="F6" s="46" t="s">
         <v>184</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="G6" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="H6" s="46"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="46"/>
+      <c r="M6" s="45" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="72">
+      <c r="A7" s="38" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+    </row>
+    <row r="8" spans="1:13" ht="158.4">
+      <c r="A8" s="40" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="43" t="s">
         <v>186</v>
       </c>
-      <c r="L1" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="27" t="s">
+      <c r="C8" s="43" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-    </row>
-    <row r="3" spans="1:13" ht="205.2">
-      <c r="A3" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="D8" s="43" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="E8" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="F8" s="43" t="s">
         <v>190</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="G8" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="H8" s="43"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="118.8">
+      <c r="A9" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="E9" s="46" t="s">
         <v>193</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="239.4">
-      <c r="A4" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="30" t="s">
+      <c r="F9" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="G9" s="46" t="s">
         <v>195</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="H9" s="46"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="84">
+      <c r="A10" s="38" t="s">
+        <v>318</v>
+      </c>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+    </row>
+    <row r="11" spans="1:13" ht="118.8">
+      <c r="A11" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="C11" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="26" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="27" t="s">
+      <c r="D11" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-    </row>
-    <row r="6" spans="1:13" ht="205.2">
-      <c r="A6" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="29" t="s">
+      <c r="E11" s="43" t="s">
         <v>199</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="F11" s="43" t="s">
         <v>200</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="G11" s="43" t="s">
         <v>201</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="H11" s="43"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="43"/>
+      <c r="M11" s="44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="84">
+      <c r="A12" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+    </row>
+    <row r="13" spans="1:13" ht="145.19999999999999">
+      <c r="A13" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B13" s="41" t="s">
         <v>202</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="C13" s="41" t="s">
         <v>203</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="D13" s="41" t="s">
         <v>204</v>
       </c>
-      <c r="H6" s="30"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="228">
-      <c r="A7" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="30" t="s">
+      <c r="E13" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="F13" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="F7" s="30" t="s">
+      <c r="G13" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="H13" s="41"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="132">
+      <c r="A14" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" s="47" t="s">
         <v>208</v>
       </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="27" t="s">
+      <c r="E14" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-    </row>
-    <row r="9" spans="1:13" ht="307.8">
-      <c r="A9" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="29" t="s">
+      <c r="F14" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="G14" s="47" t="s">
         <v>211</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="H14" s="47"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="48" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="84">
+      <c r="A15" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+    </row>
+    <row r="16" spans="1:13" ht="145.19999999999999">
+      <c r="A16" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="C16" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="D16" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="E16" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="H9" s="30"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="228">
-      <c r="A10" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" s="30" t="s">
+      <c r="F16" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="G16" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="H16" s="41"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="40" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="84">
+      <c r="A17" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+    </row>
+    <row r="18" spans="1:13" ht="118.8">
+      <c r="A18" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="41" t="s">
         <v>218</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="C18" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="H10" s="30"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="27" t="s">
+      <c r="D18" s="41" t="s">
         <v>220</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="28"/>
-    </row>
-    <row r="12" spans="1:13" ht="228">
-      <c r="A12" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="29" t="s">
+      <c r="E18" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="F18" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="G18" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="H18" s="41"/>
+      <c r="I18" s="40"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="40"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="60">
+      <c r="A19" s="38" t="s">
+        <v>322</v>
+      </c>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+    </row>
+    <row r="20" spans="1:13" ht="118.8">
+      <c r="A20" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" s="43" t="s">
         <v>224</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="C20" s="43" t="s">
         <v>225</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="D20" s="43" t="s">
         <v>226</v>
       </c>
-      <c r="H12" s="30"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="239.4">
-      <c r="A13" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="D13" s="30" t="s">
+      <c r="E20" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="43" t="s">
         <v>227</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="G20" s="43" t="s">
         <v>228</v>
       </c>
-      <c r="F13" s="30" t="s">
+      <c r="H20" s="43"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="44" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="84">
+      <c r="A21" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+    </row>
+    <row r="22" spans="1:13" ht="132">
+      <c r="A22" s="40" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="C22" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="H13" s="30"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="27" t="s">
+      <c r="D22" s="41" t="s">
         <v>231</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-      <c r="M14" s="28"/>
-    </row>
-    <row r="15" spans="1:13" ht="250.8">
-      <c r="A15" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="B15" s="29" t="s">
+      <c r="E22" s="41" t="s">
         <v>232</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="F22" s="41" t="s">
         <v>233</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="G22" s="41" t="s">
         <v>234</v>
       </c>
-      <c r="E15" s="30" t="s">
+      <c r="H22" s="41"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="40" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="105.6">
+      <c r="A23" s="45" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="C23" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="D23" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="F15" s="30" t="s">
+      <c r="E23" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="G15" s="30" t="s">
+      <c r="F23" s="47" t="s">
+        <v>324</v>
+      </c>
+      <c r="G23" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="239.4">
-      <c r="A16" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>232</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="D16" s="30" t="s">
+      <c r="H23" s="47"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="48" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="84">
+      <c r="A24" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+    </row>
+    <row r="25" spans="1:13" ht="145.19999999999999">
+      <c r="A25" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="41" t="s">
         <v>238</v>
       </c>
-      <c r="E16" s="30" t="s">
+      <c r="C25" s="41" t="s">
         <v>239</v>
       </c>
-      <c r="F16" s="30" t="s">
+      <c r="D25" s="41" t="s">
         <v>240</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="E25" s="41" t="s">
         <v>241</v>
       </c>
-      <c r="H16" s="30"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="26" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="27" t="s">
+      <c r="F25" s="41" t="s">
         <v>242</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
-    </row>
-    <row r="18" spans="1:13" ht="250.8">
-      <c r="A18" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="29" t="s">
+      <c r="G25" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="H25" s="41"/>
+      <c r="I25" s="40"/>
+      <c r="J25" s="41"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="41"/>
+      <c r="M25" s="40" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="118.8">
+      <c r="A26" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="E26" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="F26" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="E18" s="30" t="s">
+      <c r="G26" s="47" t="s">
         <v>246</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="H26" s="47"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="48" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="84">
+      <c r="A27" s="38" t="s">
+        <v>326</v>
+      </c>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+    </row>
+    <row r="28" spans="1:13" ht="132">
+      <c r="A28" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="B28" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="C28" s="41" t="s">
         <v>248</v>
       </c>
-      <c r="H18" s="30"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="26" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="193.8">
-      <c r="A19" s="26" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>243</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="D19" s="30" t="s">
+      <c r="D28" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="E19" s="30" t="s">
+      <c r="E28" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F28" s="41" t="s">
         <v>251</v>
       </c>
-      <c r="G19" s="30" t="s">
+      <c r="G28" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="H19" s="30"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="26" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="27" t="s">
+      <c r="H28" s="41"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="40"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="72">
+      <c r="A29" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="39"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+    </row>
+    <row r="30" spans="1:13" ht="118.8">
+      <c r="A30" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-    </row>
-    <row r="21" spans="1:13" ht="216.6">
-      <c r="A21" s="26" t="s">
-        <v>107</v>
-      </c>
-      <c r="B21" s="29" t="s">
+      <c r="C30" s="41" t="s">
         <v>254</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="D30" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="E30" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="E21" s="30" t="s">
+      <c r="F30" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="F21" s="30" t="s">
+      <c r="G30" s="41" t="s">
         <v>258</v>
       </c>
-      <c r="G21" s="30" t="s">
+      <c r="H30" s="41"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="41"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="40" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="72">
+      <c r="A31" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="B31" s="42"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="42"/>
+    </row>
+    <row r="32" spans="1:13" ht="118.8">
+      <c r="A32" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>135</v>
+      </c>
+      <c r="C32" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="H21" s="30"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="26" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="171">
-      <c r="A22" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="D22" s="30" t="s">
+      <c r="D32" s="43" t="s">
         <v>260</v>
       </c>
-      <c r="E22" s="30" t="s">
+      <c r="E32" s="43" t="s">
         <v>261</v>
       </c>
-      <c r="F22" s="30" t="s">
+      <c r="F32" s="43" t="s">
         <v>262</v>
       </c>
-      <c r="G22" s="30" t="s">
+      <c r="G32" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="H22" s="30"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="26" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="27" t="s">
+      <c r="H32" s="43"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="43"/>
+      <c r="M32" s="44" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="84">
+      <c r="A33" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="B33" s="42"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+    </row>
+    <row r="34" spans="1:13" ht="145.19999999999999">
+      <c r="A34" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="B34" s="41" t="s">
         <v>264</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-    </row>
-    <row r="24" spans="1:13" ht="205.2">
-      <c r="A24" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" s="29" t="s">
+      <c r="C34" s="41" t="s">
         <v>265</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="D34" s="41" t="s">
         <v>266</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="E34" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="E24" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="F24" s="30" t="s">
+      <c r="F34" s="41" t="s">
         <v>268</v>
       </c>
-      <c r="G24" s="30" t="s">
+      <c r="G34" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="H24" s="30"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="182.4">
-      <c r="A25" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>265</v>
-      </c>
-      <c r="C25" s="30" t="s">
-        <v>266</v>
-      </c>
-      <c r="D25" s="30" t="s">
+      <c r="H34" s="41"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="40" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="72">
+      <c r="A35" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+    </row>
+    <row r="36" spans="1:13" ht="118.8">
+      <c r="A36" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="E25" s="30" t="s">
+      <c r="D36" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="F25" s="30" t="s">
+      <c r="E36" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="G25" s="30" t="s">
+      <c r="F36" s="41" t="s">
         <v>273</v>
       </c>
-      <c r="H25" s="30"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="30"/>
-      <c r="M25" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="27" t="s">
+      <c r="G36" s="41" t="s">
         <v>274</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-    </row>
-    <row r="27" spans="1:13" ht="228">
-      <c r="A27" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B27" s="29" t="s">
+      <c r="H36" s="41"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="41"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="41"/>
+      <c r="M36" s="40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="105.6">
+      <c r="A37" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" s="41" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D37" s="41" t="s">
         <v>275</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="E37" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="F37" s="41" t="s">
         <v>277</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="G37" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="H37" s="41"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="41"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="41"/>
+      <c r="M37" s="40" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="84">
+      <c r="A38" s="38" t="s">
+        <v>331</v>
+      </c>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
+      <c r="K38" s="39"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+    </row>
+    <row r="39" spans="1:13" ht="158.4">
+      <c r="A39" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="41" t="s">
         <v>279</v>
       </c>
-      <c r="G27" s="30" t="s">
+      <c r="C39" s="41" t="s">
         <v>280</v>
       </c>
-      <c r="H27" s="30"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="26" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="205.2">
-      <c r="A28" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="29" t="s">
-        <v>275</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="D28" s="30" t="s">
+      <c r="D39" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E39" s="41" t="s">
         <v>282</v>
       </c>
-      <c r="F28" s="30" t="s">
+      <c r="F39" s="41" t="s">
         <v>283</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G39" s="41" t="s">
         <v>284</v>
       </c>
-      <c r="H28" s="30"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="30"/>
-      <c r="M28" s="26" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-    </row>
-    <row r="30" spans="1:13" ht="262.2">
-      <c r="A30" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="B30" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>288</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="F30" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="G30" s="30" t="s">
-        <v>291</v>
-      </c>
-      <c r="H30" s="30"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="30"/>
-      <c r="M30" s="26" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="193.8">
-      <c r="A31" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="B31" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="C31" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="D31" s="30" t="s">
-        <v>292</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="F31" s="30" t="s">
-        <v>293</v>
-      </c>
-      <c r="G31" s="30" t="s">
-        <v>294</v>
-      </c>
-      <c r="H31" s="30"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="26" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-    </row>
-    <row r="33" spans="1:13" ht="205.2">
-      <c r="A33" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>298</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>299</v>
-      </c>
-      <c r="F33" s="30" t="s">
-        <v>300</v>
-      </c>
-      <c r="G33" s="30" t="s">
-        <v>301</v>
-      </c>
-      <c r="H33" s="30"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="26" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="182.4">
-      <c r="A34" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="B34" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>297</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>302</v>
-      </c>
-      <c r="E34" s="30" t="s">
-        <v>303</v>
-      </c>
-      <c r="F34" s="30" t="s">
-        <v>304</v>
-      </c>
-      <c r="G34" s="30" t="s">
-        <v>305</v>
-      </c>
-      <c r="H34" s="30"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="26" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
-      <c r="A35" s="27" t="s">
-        <v>306</v>
-      </c>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-    </row>
-    <row r="36" spans="1:13" ht="250.8">
-      <c r="A36" s="26" t="s">
+      <c r="H39" s="41"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="41"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="41"/>
+      <c r="M39" s="40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="84">
+      <c r="A40" s="56" t="s">
+        <v>370</v>
+      </c>
+      <c r="B40" s="39"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="39"/>
+      <c r="G40" s="39"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="39"/>
+      <c r="J40" s="39"/>
+      <c r="K40" s="39"/>
+      <c r="L40" s="39"/>
+      <c r="M40" s="39"/>
+    </row>
+    <row r="41" spans="1:13" ht="158.4">
+      <c r="A41" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="C36" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="D36" s="30" t="s">
-        <v>309</v>
-      </c>
-      <c r="E36" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="F36" s="30" t="s">
-        <v>311</v>
-      </c>
-      <c r="G36" s="30" t="s">
-        <v>312</v>
-      </c>
-      <c r="H36" s="30"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="30"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="30"/>
-      <c r="M36" s="26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="205.2">
-      <c r="A37" s="26" t="s">
+      <c r="B41" s="43" t="s">
+        <v>371</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>372</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>373</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>374</v>
+      </c>
+      <c r="F41" s="43" t="s">
+        <v>375</v>
+      </c>
+      <c r="G41" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
+      <c r="M41" s="44" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="72">
+      <c r="A42" s="56" t="s">
+        <v>377</v>
+      </c>
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="39"/>
+      <c r="G42" s="39"/>
+      <c r="H42" s="39"/>
+      <c r="I42" s="39"/>
+      <c r="J42" s="39"/>
+      <c r="K42" s="39"/>
+      <c r="L42" s="39"/>
+      <c r="M42" s="39"/>
+    </row>
+    <row r="43" spans="1:13" ht="158.4">
+      <c r="A43" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="B37" s="29" t="s">
-        <v>307</v>
-      </c>
-      <c r="C37" s="30" t="s">
-        <v>308</v>
-      </c>
-      <c r="D37" s="30" t="s">
-        <v>313</v>
-      </c>
-      <c r="E37" s="30" t="s">
-        <v>314</v>
-      </c>
-      <c r="F37" s="30" t="s">
-        <v>315</v>
-      </c>
-      <c r="G37" s="30" t="s">
-        <v>316</v>
-      </c>
-      <c r="H37" s="30"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
-      <c r="A38" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-    </row>
-    <row r="39" spans="1:13" ht="216.6">
-      <c r="A39" s="26" t="s">
+      <c r="B43" s="43" t="s">
+        <v>378</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>379</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>380</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>381</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>382</v>
+      </c>
+      <c r="G43" s="43" t="s">
+        <v>383</v>
+      </c>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="43"/>
+      <c r="M43" s="44" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="145.19999999999999">
+      <c r="A44" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="B39" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>318</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>319</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>320</v>
-      </c>
-      <c r="F39" s="30" t="s">
-        <v>321</v>
-      </c>
-      <c r="G39" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="H39" s="30"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="30"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="30"/>
-      <c r="M39" s="26" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="205.2">
-      <c r="A40" s="26" t="s">
+      <c r="B44" s="43" t="s">
+        <v>378</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>379</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>384</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>385</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>386</v>
+      </c>
+      <c r="G44" s="43" t="s">
+        <v>387</v>
+      </c>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="43"/>
+      <c r="L44" s="43"/>
+      <c r="M44" s="44" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="72">
+      <c r="A45" s="56" t="s">
+        <v>388</v>
+      </c>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="39"/>
+      <c r="J45" s="39"/>
+      <c r="K45" s="39"/>
+      <c r="L45" s="39"/>
+      <c r="M45" s="39"/>
+    </row>
+    <row r="46" spans="1:13" ht="184.8">
+      <c r="A46" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="B40" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>318</v>
-      </c>
-      <c r="D40" s="30" t="s">
-        <v>323</v>
-      </c>
-      <c r="E40" s="30" t="s">
-        <v>324</v>
-      </c>
-      <c r="F40" s="30" t="s">
-        <v>325</v>
-      </c>
-      <c r="G40" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="H40" s="30"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="26" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
-      <c r="A41" s="27" t="s">
-        <v>327</v>
-      </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-    </row>
-    <row r="42" spans="1:13" ht="239.4">
-      <c r="A42" s="26" t="s">
+      <c r="B46" s="43" t="s">
+        <v>389</v>
+      </c>
+      <c r="C46" s="43" t="s">
+        <v>390</v>
+      </c>
+      <c r="D46" s="43" t="s">
+        <v>391</v>
+      </c>
+      <c r="E46" s="43" t="s">
+        <v>392</v>
+      </c>
+      <c r="F46" s="43" t="s">
+        <v>393</v>
+      </c>
+      <c r="G46" s="43" t="s">
+        <v>394</v>
+      </c>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="43"/>
+      <c r="M46" s="44" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="158.4">
+      <c r="A47" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="B42" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>329</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>330</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>331</v>
-      </c>
-      <c r="F42" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="G42" s="30" t="s">
-        <v>333</v>
-      </c>
-      <c r="H42" s="30"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="30"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="30"/>
-      <c r="M42" s="26" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="216.6">
-      <c r="A43" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B43" s="29" t="s">
-        <v>328</v>
-      </c>
-      <c r="C43" s="30" t="s">
-        <v>329</v>
-      </c>
-      <c r="D43" s="30" t="s">
-        <v>334</v>
-      </c>
-      <c r="E43" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="F43" s="30" t="s">
-        <v>336</v>
-      </c>
-      <c r="G43" s="30" t="s">
-        <v>337</v>
-      </c>
-      <c r="H43" s="30"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="26" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
-      <c r="A44" s="27" t="s">
-        <v>338</v>
-      </c>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-    </row>
-    <row r="45" spans="1:13" ht="216.6">
-      <c r="A45" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="B45" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="D45" s="30" t="s">
-        <v>340</v>
-      </c>
-      <c r="E45" s="30" t="s">
-        <v>341</v>
-      </c>
-      <c r="F45" s="30" t="s">
-        <v>342</v>
-      </c>
-      <c r="G45" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="H45" s="30"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="30"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="30"/>
-      <c r="M45" s="26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="193.8">
-      <c r="A46" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="B46" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="C46" s="30" t="s">
-        <v>339</v>
-      </c>
-      <c r="D46" s="30" t="s">
-        <v>344</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>345</v>
-      </c>
-      <c r="F46" s="30" t="s">
-        <v>346</v>
-      </c>
-      <c r="G46" s="30" t="s">
-        <v>347</v>
-      </c>
-      <c r="H46" s="30"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="A47" s="27" t="s">
-        <v>348</v>
-      </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="28"/>
-      <c r="M47" s="28"/>
-    </row>
-    <row r="48" spans="1:13" ht="262.2">
-      <c r="A48" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="B48" s="29" t="s">
-        <v>349</v>
-      </c>
-      <c r="C48" s="30" t="s">
-        <v>350</v>
-      </c>
-      <c r="D48" s="30" t="s">
-        <v>351</v>
-      </c>
-      <c r="E48" s="30" t="s">
-        <v>352</v>
-      </c>
-      <c r="F48" s="30" t="s">
-        <v>353</v>
-      </c>
-      <c r="G48" s="30" t="s">
-        <v>354</v>
-      </c>
-      <c r="H48" s="30"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="26" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="250.8">
-      <c r="A49" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="B49" s="29" t="s">
-        <v>349</v>
-      </c>
-      <c r="C49" s="30" t="s">
-        <v>350</v>
-      </c>
-      <c r="D49" s="30" t="s">
-        <v>355</v>
-      </c>
-      <c r="E49" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="F49" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="G49" s="30" t="s">
-        <v>357</v>
-      </c>
-      <c r="H49" s="30"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="26" t="s">
-        <v>146</v>
+      <c r="B47" s="43" t="s">
+        <v>389</v>
+      </c>
+      <c r="C47" s="43" t="s">
+        <v>395</v>
+      </c>
+      <c r="D47" s="43" t="s">
+        <v>396</v>
+      </c>
+      <c r="E47" s="43" t="s">
+        <v>397</v>
+      </c>
+      <c r="F47" s="43" t="s">
+        <v>398</v>
+      </c>
+      <c r="G47" s="43" t="s">
+        <v>399</v>
+      </c>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="43"/>
+      <c r="M47" s="44" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A47:M47"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A41:M41"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="A44:M44"/>
-    <mergeCell ref="A26:M26"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
